--- a/extenbooks/S407_extenbook.xlsx
+++ b/extenbooks/S407_extenbook.xlsx
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1223,14 +1223,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**Data Provenance Record (DPR)**</t>
+          <t>**Data Provenance Record (DPR)** — the internal, full-provenance companion to the public Explainer.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Record type**: Data Provenance Record (source-and-construction detail)</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>&gt; **Recovery (2026-05-26):** Recovered from data_unavailable by native-resolution vector trace of Shaikh Fig 4.22 Marginal Cost (= Inman 1995) from the book PDF (Robert _PDF_LIBRARY p204-205), overlay-validated vs the figure. content_type=theoretical (Monte-Carlo simulation curve), x=annual vehicle output; chopped keys on point-index per the S308 functional-curve precedent. provenance: digitized. V03 round-trip PASS; pipeline + anu-doctor 0/0. Source: SalvagedInputs/book_data/Reconstructed/Inman_1995_S404-407_cost_curves.json; method: Technical/WL1_Tsoulfidis_Tsaliki/EXTRACTION_REPORT.md.</t>
+          <t>&gt; **Recovery (2026-05-26):** This curve was previously marked as having no available underlying data. It was recovered by digitizing Shaikh's Figure 4.22 (Marginal Cost, which reproduces Inman 1995) from the source-book scan at native resolution, then overlay-checking the digitized points against the printed figure. It is a theoretical curve (the mean of a Monte-Carlo plant simulation); the horizontal axis is annual vehicle output (not calendar years), and the points are ordered by an index number. The validation step reproduces the digitized values, and the project self-audit passes. Reconstructed points: `SalvagedInputs/book_data/Reconstructed/Inman_1995_S404-407_cost_curves.json`.</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch4-fanout</t>
+          <t>**Prepared by**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>This is Shaikh's culminating empirical exhibit for the chapter's central argument against `p = mc`. Per p. 161: "The rule p = mc would then select a very large number of points if p happened to run along the flat bottom of the curve; would select multiple points, including engineering capacity, if p was between this lower limit and the tops of various spikes; and would select only engineering capacity if p was higher still." The flat-bottom-with-spikes shape — empirically observed in Inman's simulation — destroys the unique-output interpretation of `p = mc`.</t>
+          <t>This is Shaikh's culminating empirical exhibit for the chapter's central argument against the neoclassical `price = marginal cost` rule. Per p. 161: "The rule p = mc would then select a very large number of points if p happened to run along the flat bottom of the curve; would select multiple points, including engineering capacity, if p was between this lower limit and the tops of various spikes; and would select only engineering capacity if p was higher still." The flat-bottom-with-spikes shape — empirically observed in Inman's simulation — destroys the unique-output interpretation of `price = marginal cost`.</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>## 3. Sources (per subseries)</t>
+          <t>## From the Book</t>
         </is>
       </c>
     </row>
@@ -1348,202 +1348,198 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher | Native units | Retrieval |</t>
+          <t>&gt; the overall marginal cost curve is essentially flat-bottomed over much of the observed range of output, with modest spikes at each new shift.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>|---|---|---|---|---|</t>
+          <t>&gt; -- Shaikh (2016), Chapter 4, p. 161 &lt;!-- kb: ch04, p.161 (ch04_production_costs.md, Automotive Marginal Cost, Fig 4.22) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>| **S407-A** | output range 0–~450 thousand vehicles/year | Inman, R. R. (1995), *The Engineering Economist* 41(1), 53–67, fig. 6 | USD per additional car | **NOT RETRIEVABLE** (paywall) |</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Verified verbatim against the project knowledge-base extraction of the source book (`ch04_production_costs.md`).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>## 4. Construction</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>## 3. Sources (per subseries)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>`mc(Q) = c_material + mlc(Q)` (constant material cost). `mlc` from S405. Inman fig. 6 shows the combined curve.</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>| Subseries | Coverage | Publisher | Native units | Retrieval |</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>|---|---|---|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>| **S407-A** (the dataset's single data column) | output range 0–~450 thousand vehicles/year | Inman, R. R. (1995), *The Engineering Economist* 41(1), 53–67, fig. 6 | USD per additional car | **Recovered by figure digitization** of Shaikh's Fig 4.22 (reproducing Inman's fig. 6), overlay-validated against the printed figure |</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>## 4. Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>`mc(Q) = c_material + mlc(Q)` (constant material cost). `mlc` from S405. Inman fig. 6 shows the combined curve. The curve was recovered by digitizing Shaikh's Fig 4.22 reproduction (stored in `Inman_1995_S404-407_cost_curves.json`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Not applicable.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>## 6. Units</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>USD per additional car. Y-axis range ~$0–$8,000 in fig. 6 — material-cost flat bottom dominates, with modest labor-cost spikes at shift changes.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Identical to S404 — `data_unavailable`. No figure digitization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Same recovery posture as S404: previously marked as having no available data, now recovered by figure digitization of Shaikh's reproduction and overlay-validated. Digitization from figures is the project's documented last-resort recovery method when exact values cannot be obtained otherwise; this is not a proxy or fabricated series. Citation confirmed as Robert R. Inman (1995).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>- **Cross-series**: S405 (mlc input), S406 (ac twin), S402 (theoretical analogue under per-hour wages).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>- **Predecessor series**: none (first constructed in this dataset)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>- **Cross-series**: S405 (marginal labour-cost input), S406 (average-cost twin), S402 (theoretical analogue under per-hour wages).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>## 9. Validation expectation</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>`PASS_DATA_UNAVAILABLE`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4">
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>The validation step reproduces the digitized curve from the stored reconstruction and confirms the processed data match it (a round-trip check); because the source is a digitized figure rather than a published table, the check verifies faithful reproduction of the digitized points and shape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4">
         <f>== EPR: S407_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t># S407 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>**Series**: S407 — Automotive Marginal Cost (Fig 4.22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `derived` / `data_unavailable`</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>**Extension method**: **not_applicable_theoretical**</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-    </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>---</t>
+          <t># S407 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1549,55 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Identical reasoning to S404_EPR. Inman 1995 paywall + cross-section. No extension.</t>
+          <t>**Series**: S407 — Automotive Marginal Cost (Fig 4.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>**Record type**: Extension Provenance Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>**Construction classification**: `derived` (theoretical Monte-Carlo simulation curve)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>**Extension method**: **not_applicable_theoretical**</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Identical reasoning to S404_EPR. The curve was recovered on 2026-05-26 by digitizing Shaikh's Fig 4.22 — which reproduces Inman (1995), *The Engineering Economist* 41(1):53-67, fig. 6 — and overlay-validated against the printed figure; the reconstructed points are stored among the project's salvaged reconstructions. The curve plots cost against annual vehicle output (in thousands), not calendar time, so no time-series extension applies. No extension; no proxy; no synthetic data in the prohibited sense (a faithful trace of the source's own printed curve); no predecessor series (first constructed in this dataset). (An earlier version of this record described the series as unavailable; that is superseded by the figure-digitization recovery.)</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1830,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-26T23:36:10.145573+00:00</t>
+          <t>2026-07-02T06:23:53.301659+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S407_extenbook.xlsx
+++ b/extenbooks/S407_extenbook.xlsx
@@ -1254,7 +1254,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>&gt; **Recovery (2026-05-26):** This curve was previously marked as having no available underlying data. It was recovered by digitizing Shaikh's Figure 4.22 (Marginal Cost, which reproduces Inman 1995) from the source-book scan at native resolution, then overlay-checking the digitized points against the printed figure. It is a theoretical curve (the mean of a Monte-Carlo plant simulation); the horizontal axis is annual vehicle output (not calendar years), and the points are ordered by an index number. The validation step reproduces the digitized values, and the project self-audit passes. Reconstructed points: `SalvagedInputs/book_data/Reconstructed/Inman_1995_S404-407_cost_curves.json`.</t>
+          <t>&gt; **Recovery (2026-05-26):** This curve was previously marked as having no available underlying data. It was recovered by digitizing Shaikh's Figure 4.22 (Marginal Cost, which reproduces Inman 1995) via native-vector trace of the book PDF (PyMuPDF `get_drawings`), then overlay-checking the digitized points against the printed figure. It is a theoretical curve (the mean of a Monte-Carlo plant simulation); the horizontal axis is annual vehicle output (not calendar years), and the points are ordered by an index number. The validation step reproduces the digitized values, and the project self-audit passes. Reconstructed points: `SalvagedInputs/book_data/Reconstructed/Inman_1995_S404-407_cost_curves.json`. Extraction workbench: `Technical/WL1_Tsoulfidis_Tsaliki/` (overlays: `inman_S407_native.png`, `inman_S407_overlay.png`). &lt;!-- F-7C-03 + F-5F-07: 'source-book scan at native resolution' → 'native-vector trace'; workbench pointer added 2026-07-10 --&gt;</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-02T06:23:53.301659+00:00</t>
+          <t>2026-07-11T03:44:24.888081+00:00</t>
         </is>
       </c>
     </row>
@@ -1845,11 +1845,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1872,6 +1872,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INMAN_1995_ENGINEERING_ECONOMIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Renderable cost curve (Shaikh Fig 4.22): overall marginal cost per additional car vs annual vehicle production, digitized from Inman (1995) via Shaikh. 17 non-null points, single subseries. Renders as an x-y curve (x = annual vehicle output in thousands, 'year' index column, NOT calendar years). L01/P02 exist; replicate.py builds it (PASS). content_type derived. KB coverage: ch04 IS extracted in the book KB (HDARP v3.3 Sraffa OCR campaign) (Body_Text/ch04_production_costs.md + Figures/ch04/ch04_figure_4.22.md); the chapter-4 figure quotes in the research JSON ARE verifiable against KB, and a 'From the book' section can be populated in the explainer (doc-side backfill).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S407_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S407_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Inman 1995 fig. 6. RECOVERED 2026-05-26 by native-vector tracing of Shaikh Fig 4.22 (provenance: digitized); flipped off data_unavailable. Constructionally mc = c_material + S405. Citation: Inman, R. R. (1995), 'Shape Characteristics of Cost Curves Involving Multiple Shifts in Automotive Assembly Plants,' The Engineering Economist 41(1), 53-67, DOI 10.1080/00137919508967475 (Crossref-verified; supersedes the withdrawn 'How to Have a Fiscal Crisis' attribution).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>USD per additional car vs. annual vehicle production (thousands)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
